--- a/artfynd/A 56674-2020 artfynd.xlsx
+++ b/artfynd/A 56674-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 56674-2020 artfynd.xlsx
+++ b/artfynd/A 56674-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>95263400</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -735,10 +735,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>553300.55764852</v>
+        <v>553301</v>
       </c>
       <c r="R2" t="n">
-        <v>6835184.143786674</v>
+        <v>6835184</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -768,19 +768,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,12 +786,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -811,7 +801,7 @@
         <v>95264460</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -868,10 +858,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>553241.2079668331</v>
+        <v>553241</v>
       </c>
       <c r="R3" t="n">
-        <v>6835143.300850938</v>
+        <v>6835143</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,19 +891,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -939,12 +919,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -954,7 +934,7 @@
         <v>95264089</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1011,10 +991,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>553285.4370830621</v>
+        <v>553285</v>
       </c>
       <c r="R4" t="n">
-        <v>6835207.675594461</v>
+        <v>6835208</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1044,19 +1024,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1082,12 +1052,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1097,7 +1067,7 @@
         <v>95264522</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1154,10 +1124,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>553269.3022117999</v>
+        <v>553269</v>
       </c>
       <c r="R5" t="n">
-        <v>6835142.783994451</v>
+        <v>6835143</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1187,19 +1157,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1225,12 +1185,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1240,7 +1200,7 @@
         <v>95264049</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1297,10 +1257,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>553290.4739242411</v>
+        <v>553290</v>
       </c>
       <c r="R6" t="n">
-        <v>6835220.586682212</v>
+        <v>6835221</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1330,19 +1290,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1368,12 +1318,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1383,7 +1333,7 @@
         <v>95264194</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1440,10 +1390,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>553285.1874783114</v>
+        <v>553285</v>
       </c>
       <c r="R7" t="n">
-        <v>6835223.832143187</v>
+        <v>6835224</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1473,19 +1423,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1511,12 +1451,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1526,7 +1466,7 @@
         <v>95264257</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1583,10 +1523,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>553278.0928131961</v>
+        <v>553278</v>
       </c>
       <c r="R8" t="n">
-        <v>6835220.870713392</v>
+        <v>6835221</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1616,19 +1556,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1654,12 +1584,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1669,7 +1599,7 @@
         <v>95263872</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1726,10 +1656,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>553297.5479298893</v>
+        <v>553298</v>
       </c>
       <c r="R9" t="n">
-        <v>6835194.078782379</v>
+        <v>6835194</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1759,19 +1689,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1797,12 +1717,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1812,7 +1732,7 @@
         <v>95386244</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1865,10 +1785,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>553144.3462572343</v>
+        <v>553144</v>
       </c>
       <c r="R10" t="n">
-        <v>6835157.96774963</v>
+        <v>6835158</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1898,19 +1818,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1926,12 +1836,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1941,7 +1851,7 @@
         <v>95386183</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1994,10 +1904,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>553168.0032188112</v>
+        <v>553168</v>
       </c>
       <c r="R11" t="n">
-        <v>6835167.363277408</v>
+        <v>6835167</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2027,19 +1937,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2055,12 +1955,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2070,7 +1970,7 @@
         <v>95386114</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2123,10 +2023,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>553307.2043658107</v>
+        <v>553307</v>
       </c>
       <c r="R12" t="n">
-        <v>6835216.092161599</v>
+        <v>6835216</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2156,19 +2056,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2189,12 +2079,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2204,7 +2094,7 @@
         <v>95386099</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2257,10 +2147,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>553304.4737235887</v>
+        <v>553304</v>
       </c>
       <c r="R13" t="n">
-        <v>6835207.969746494</v>
+        <v>6835208</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2290,19 +2180,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2318,12 +2198,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2333,7 +2213,7 @@
         <v>95386259</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2386,10 +2266,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>553128.9337335289</v>
+        <v>553129</v>
       </c>
       <c r="R14" t="n">
-        <v>6835169.613119329</v>
+        <v>6835170</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2419,19 +2299,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2447,12 +2317,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2462,7 +2332,7 @@
         <v>95386456</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2515,10 +2385,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>553247.8406454186</v>
+        <v>553248</v>
       </c>
       <c r="R15" t="n">
-        <v>6835176.199872245</v>
+        <v>6835176</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2548,19 +2418,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2581,12 +2441,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2596,7 +2456,7 @@
         <v>95386154</v>
       </c>
       <c r="B16" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2649,10 +2509,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>553256.256400865</v>
+        <v>553256</v>
       </c>
       <c r="R16" t="n">
-        <v>6835309.414410581</v>
+        <v>6835309</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2682,19 +2542,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2715,12 +2565,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2730,7 +2580,7 @@
         <v>95386313</v>
       </c>
       <c r="B17" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2783,10 +2633,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>553052.3972968218</v>
+        <v>553052</v>
       </c>
       <c r="R17" t="n">
-        <v>6835131.835866421</v>
+        <v>6835132</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2816,19 +2666,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2849,12 +2689,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2864,7 +2704,7 @@
         <v>95386133</v>
       </c>
       <c r="B18" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2917,10 +2757,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>553305.2566418765</v>
+        <v>553305</v>
       </c>
       <c r="R18" t="n">
-        <v>6835218.913894441</v>
+        <v>6835219</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2950,19 +2790,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2983,12 +2813,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2998,7 +2828,7 @@
         <v>95386487</v>
       </c>
       <c r="B19" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3051,10 +2881,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>553257.8202975453</v>
+        <v>553258</v>
       </c>
       <c r="R19" t="n">
-        <v>6835177.304575486</v>
+        <v>6835177</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3084,19 +2914,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3112,12 +2932,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -3127,7 +2947,7 @@
         <v>95264356</v>
       </c>
       <c r="B20" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3184,10 +3004,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>553079.5999635729</v>
+        <v>553080</v>
       </c>
       <c r="R20" t="n">
-        <v>6835220.18681554</v>
+        <v>6835220</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3217,19 +3037,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3260,12 +3070,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3275,7 +3085,7 @@
         <v>95386500</v>
       </c>
       <c r="B21" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3328,10 +3138,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>553255.8359071156</v>
+        <v>553256</v>
       </c>
       <c r="R21" t="n">
-        <v>6835182.502354077</v>
+        <v>6835183</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3361,19 +3171,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3389,12 +3189,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3404,7 +3204,7 @@
         <v>95386164</v>
       </c>
       <c r="B22" t="n">
-        <v>93044</v>
+        <v>94771</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3445,10 +3245,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>553236.4648461207</v>
+        <v>553236</v>
       </c>
       <c r="R22" t="n">
-        <v>6835358.063690718</v>
+        <v>6835358</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3478,19 +3278,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3506,12 +3296,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3521,7 +3311,7 @@
         <v>95264703</v>
       </c>
       <c r="B23" t="n">
-        <v>93044</v>
+        <v>94771</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3570,10 +3360,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>553102.4785238563</v>
+        <v>553102</v>
       </c>
       <c r="R23" t="n">
-        <v>6835063.68494942</v>
+        <v>6835064</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3603,19 +3393,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3641,12 +3421,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3656,7 +3436,7 @@
         <v>95264424</v>
       </c>
       <c r="B24" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3713,10 +3493,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>553092.8057177188</v>
+        <v>553093</v>
       </c>
       <c r="R24" t="n">
-        <v>6835042.621640898</v>
+        <v>6835043</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3746,19 +3526,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3784,12 +3554,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3799,7 +3569,7 @@
         <v>95386390</v>
       </c>
       <c r="B25" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3852,10 +3622,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>553215.3540575525</v>
+        <v>553215</v>
       </c>
       <c r="R25" t="n">
-        <v>6835152.883483743</v>
+        <v>6835153</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3885,19 +3655,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3913,12 +3673,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3928,7 +3688,7 @@
         <v>95386224</v>
       </c>
       <c r="B26" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3981,10 +3741,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>553160.2494580678</v>
+        <v>553160</v>
       </c>
       <c r="R26" t="n">
-        <v>6835145.379338398</v>
+        <v>6835145</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4014,19 +3774,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4047,12 +3797,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -4062,7 +3812,7 @@
         <v>95386517</v>
       </c>
       <c r="B27" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4115,10 +3865,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>553279.5437942485</v>
+        <v>553280</v>
       </c>
       <c r="R27" t="n">
-        <v>6835188.572216306</v>
+        <v>6835189</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4148,19 +3898,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4181,12 +3921,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -4196,7 +3936,7 @@
         <v>95263753</v>
       </c>
       <c r="B28" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4253,10 +3993,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>553296.6181226404</v>
+        <v>553297</v>
       </c>
       <c r="R28" t="n">
-        <v>6835192.638487128</v>
+        <v>6835193</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4286,19 +4026,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4329,12 +4059,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4344,7 +4074,7 @@
         <v>95386200</v>
       </c>
       <c r="B29" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4397,10 +4127,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>553166.1801062527</v>
+        <v>553166</v>
       </c>
       <c r="R29" t="n">
-        <v>6835162.106737893</v>
+        <v>6835162</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4430,19 +4160,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4458,12 +4178,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4473,7 +4193,7 @@
         <v>95386375</v>
       </c>
       <c r="B30" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4526,10 +4246,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>553199.8176473408</v>
+        <v>553200</v>
       </c>
       <c r="R30" t="n">
-        <v>6835110.815906374</v>
+        <v>6835111</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4559,19 +4279,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4587,12 +4297,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4602,7 +4312,7 @@
         <v>97976738</v>
       </c>
       <c r="B31" t="n">
-        <v>78527</v>
+        <v>79812</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4650,10 +4360,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>553143.9215631348</v>
+        <v>553144</v>
       </c>
       <c r="R31" t="n">
-        <v>6835092.842674972</v>
+        <v>6835093</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4683,19 +4393,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4726,12 +4426,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>

--- a/artfynd/A 56674-2020 artfynd.xlsx
+++ b/artfynd/A 56674-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>95263400</v>
       </c>
       <c r="B2" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -801,7 +801,7 @@
         <v>95264460</v>
       </c>
       <c r="B3" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -919,12 +919,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -934,7 +934,7 @@
         <v>95264089</v>
       </c>
       <c r="B4" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1052,12 +1052,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1067,7 +1067,7 @@
         <v>95264522</v>
       </c>
       <c r="B5" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1185,12 +1185,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1200,7 +1200,7 @@
         <v>95264049</v>
       </c>
       <c r="B6" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1318,12 +1318,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1333,7 +1333,7 @@
         <v>95264194</v>
       </c>
       <c r="B7" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1451,12 +1451,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1466,7 +1466,7 @@
         <v>95264257</v>
       </c>
       <c r="B8" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1584,12 +1584,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1599,7 +1599,7 @@
         <v>95263872</v>
       </c>
       <c r="B9" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1717,12 +1717,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1732,7 +1732,7 @@
         <v>95386244</v>
       </c>
       <c r="B10" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1836,12 +1836,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1851,7 +1851,7 @@
         <v>95386183</v>
       </c>
       <c r="B11" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1955,12 +1955,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1970,7 +1970,7 @@
         <v>95386114</v>
       </c>
       <c r="B12" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2079,12 +2079,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2094,7 +2094,7 @@
         <v>95386099</v>
       </c>
       <c r="B13" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2198,12 +2198,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2213,7 +2213,7 @@
         <v>95386259</v>
       </c>
       <c r="B14" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2317,12 +2317,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2332,7 +2332,7 @@
         <v>95386456</v>
       </c>
       <c r="B15" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2441,12 +2441,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2456,7 +2456,7 @@
         <v>95386154</v>
       </c>
       <c r="B16" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2565,12 +2565,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2580,7 +2580,7 @@
         <v>95386313</v>
       </c>
       <c r="B17" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2689,12 +2689,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2704,7 +2704,7 @@
         <v>95386133</v>
       </c>
       <c r="B18" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2813,12 +2813,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2828,7 +2828,7 @@
         <v>95386487</v>
       </c>
       <c r="B19" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2932,12 +2932,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2947,7 +2947,7 @@
         <v>95264356</v>
       </c>
       <c r="B20" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3070,12 +3070,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3085,7 +3085,7 @@
         <v>95386500</v>
       </c>
       <c r="B21" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3189,12 +3189,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3204,7 +3204,7 @@
         <v>95386164</v>
       </c>
       <c r="B22" t="n">
-        <v>94771</v>
+        <v>94777</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3296,12 +3296,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3311,7 +3311,7 @@
         <v>95264703</v>
       </c>
       <c r="B23" t="n">
-        <v>94771</v>
+        <v>94777</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3421,12 +3421,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3436,7 +3436,7 @@
         <v>95264424</v>
       </c>
       <c r="B24" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3554,12 +3554,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3569,7 +3569,7 @@
         <v>95386390</v>
       </c>
       <c r="B25" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3673,12 +3673,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3688,7 +3688,7 @@
         <v>95386224</v>
       </c>
       <c r="B26" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3797,12 +3797,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3812,7 +3812,7 @@
         <v>95386517</v>
       </c>
       <c r="B27" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3921,12 +3921,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3936,7 +3936,7 @@
         <v>95263753</v>
       </c>
       <c r="B28" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4059,12 +4059,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4074,7 +4074,7 @@
         <v>95386200</v>
       </c>
       <c r="B29" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4178,12 +4178,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4193,7 +4193,7 @@
         <v>95386375</v>
       </c>
       <c r="B30" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4297,12 +4297,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4312,7 +4312,7 @@
         <v>97976738</v>
       </c>
       <c r="B31" t="n">
-        <v>79812</v>
+        <v>79813</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4426,12 +4426,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>

--- a/artfynd/A 56674-2020 artfynd.xlsx
+++ b/artfynd/A 56674-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>95263400</v>
       </c>
       <c r="B2" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>95264460</v>
       </c>
       <c r="B3" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>95264089</v>
       </c>
       <c r="B4" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>95264522</v>
       </c>
       <c r="B5" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>95264049</v>
       </c>
       <c r="B6" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>95264194</v>
       </c>
       <c r="B7" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>95264257</v>
       </c>
       <c r="B8" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>95263872</v>
       </c>
       <c r="B9" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>95386244</v>
       </c>
       <c r="B10" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>95386183</v>
       </c>
       <c r="B11" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>95386114</v>
       </c>
       <c r="B12" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>95386099</v>
       </c>
       <c r="B13" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>95386259</v>
       </c>
       <c r="B14" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>95386456</v>
       </c>
       <c r="B15" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>95386154</v>
       </c>
       <c r="B16" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>95386313</v>
       </c>
       <c r="B17" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>95386133</v>
       </c>
       <c r="B18" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>95386487</v>
       </c>
       <c r="B19" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>95264356</v>
       </c>
       <c r="B20" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>95386500</v>
       </c>
       <c r="B21" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>95386164</v>
       </c>
       <c r="B22" t="n">
-        <v>94777</v>
+        <v>94780</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>95264703</v>
       </c>
       <c r="B23" t="n">
-        <v>94777</v>
+        <v>94780</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>95264424</v>
       </c>
       <c r="B24" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>95386390</v>
       </c>
       <c r="B25" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>95386224</v>
       </c>
       <c r="B26" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>95386517</v>
       </c>
       <c r="B27" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>95263753</v>
       </c>
       <c r="B28" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>95386200</v>
       </c>
       <c r="B29" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>95386375</v>
       </c>
       <c r="B30" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>97976738</v>
       </c>
       <c r="B31" t="n">
-        <v>79813</v>
+        <v>79816</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 56674-2020 artfynd.xlsx
+++ b/artfynd/A 56674-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>95263400</v>
       </c>
       <c r="B2" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>95264460</v>
       </c>
       <c r="B3" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>95264089</v>
       </c>
       <c r="B4" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>95264522</v>
       </c>
       <c r="B5" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>95264049</v>
       </c>
       <c r="B6" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>95264194</v>
       </c>
       <c r="B7" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>95264257</v>
       </c>
       <c r="B8" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>95263872</v>
       </c>
       <c r="B9" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>95386244</v>
       </c>
       <c r="B10" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>95386183</v>
       </c>
       <c r="B11" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>95386114</v>
       </c>
       <c r="B12" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>95386099</v>
       </c>
       <c r="B13" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>95386259</v>
       </c>
       <c r="B14" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>95386456</v>
       </c>
       <c r="B15" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>95386154</v>
       </c>
       <c r="B16" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>95386313</v>
       </c>
       <c r="B17" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>95386133</v>
       </c>
       <c r="B18" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>95386487</v>
       </c>
       <c r="B19" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>95264356</v>
       </c>
       <c r="B20" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>95386500</v>
       </c>
       <c r="B21" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>95386164</v>
       </c>
       <c r="B22" t="n">
-        <v>94780</v>
+        <v>94797</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>95264703</v>
       </c>
       <c r="B23" t="n">
-        <v>94780</v>
+        <v>94797</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>95264424</v>
       </c>
       <c r="B24" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>95386390</v>
       </c>
       <c r="B25" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>95386224</v>
       </c>
       <c r="B26" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>95386517</v>
       </c>
       <c r="B27" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>95263753</v>
       </c>
       <c r="B28" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>95386200</v>
       </c>
       <c r="B29" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>95386375</v>
       </c>
       <c r="B30" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>97976738</v>
       </c>
       <c r="B31" t="n">
-        <v>79816</v>
+        <v>79822</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 56674-2020 artfynd.xlsx
+++ b/artfynd/A 56674-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>95263400</v>
       </c>
       <c r="B2" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>95264460</v>
       </c>
       <c r="B3" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>95264089</v>
       </c>
       <c r="B4" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>95264522</v>
       </c>
       <c r="B5" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>95264049</v>
       </c>
       <c r="B6" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>95264194</v>
       </c>
       <c r="B7" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>95264257</v>
       </c>
       <c r="B8" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>95263872</v>
       </c>
       <c r="B9" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>95386244</v>
       </c>
       <c r="B10" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>95386183</v>
       </c>
       <c r="B11" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>95386114</v>
       </c>
       <c r="B12" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>95386099</v>
       </c>
       <c r="B13" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>95386259</v>
       </c>
       <c r="B14" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>95386456</v>
       </c>
       <c r="B15" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>95386154</v>
       </c>
       <c r="B16" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>95386313</v>
       </c>
       <c r="B17" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>95386133</v>
       </c>
       <c r="B18" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>95386487</v>
       </c>
       <c r="B19" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>95264356</v>
       </c>
       <c r="B20" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>95386500</v>
       </c>
       <c r="B21" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>95386164</v>
       </c>
       <c r="B22" t="n">
-        <v>94797</v>
+        <v>94803</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>95264703</v>
       </c>
       <c r="B23" t="n">
-        <v>94797</v>
+        <v>94803</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>95264424</v>
       </c>
       <c r="B24" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>95386390</v>
       </c>
       <c r="B25" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>95386224</v>
       </c>
       <c r="B26" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>95386517</v>
       </c>
       <c r="B27" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>95263753</v>
       </c>
       <c r="B28" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>95386200</v>
       </c>
       <c r="B29" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>95386375</v>
       </c>
       <c r="B30" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>97976738</v>
       </c>
       <c r="B31" t="n">
-        <v>79822</v>
+        <v>79827</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 56674-2020 artfynd.xlsx
+++ b/artfynd/A 56674-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>95263400</v>
       </c>
       <c r="B2" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>95264460</v>
       </c>
       <c r="B3" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>95264089</v>
       </c>
       <c r="B4" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>95264522</v>
       </c>
       <c r="B5" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>95264049</v>
       </c>
       <c r="B6" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>95264194</v>
       </c>
       <c r="B7" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>95264257</v>
       </c>
       <c r="B8" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>95263872</v>
       </c>
       <c r="B9" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>95386244</v>
       </c>
       <c r="B10" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>95386183</v>
       </c>
       <c r="B11" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>95386114</v>
       </c>
       <c r="B12" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>95386099</v>
       </c>
       <c r="B13" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>95386259</v>
       </c>
       <c r="B14" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>95386456</v>
       </c>
       <c r="B15" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>95386154</v>
       </c>
       <c r="B16" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>95386313</v>
       </c>
       <c r="B17" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>95386133</v>
       </c>
       <c r="B18" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>95386487</v>
       </c>
       <c r="B19" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>95264356</v>
       </c>
       <c r="B20" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>95386500</v>
       </c>
       <c r="B21" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>95386164</v>
       </c>
       <c r="B22" t="n">
-        <v>94803</v>
+        <v>94805</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>95264703</v>
       </c>
       <c r="B23" t="n">
-        <v>94803</v>
+        <v>94805</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>95264424</v>
       </c>
       <c r="B24" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>95386390</v>
       </c>
       <c r="B25" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>95386224</v>
       </c>
       <c r="B26" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>95386517</v>
       </c>
       <c r="B27" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>95263753</v>
       </c>
       <c r="B28" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>95386200</v>
       </c>
       <c r="B29" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>95386375</v>
       </c>
       <c r="B30" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>97976738</v>
       </c>
       <c r="B31" t="n">
-        <v>79827</v>
+        <v>79829</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 56674-2020 artfynd.xlsx
+++ b/artfynd/A 56674-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>95263400</v>
       </c>
       <c r="B2" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>95264460</v>
       </c>
       <c r="B3" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>95264089</v>
       </c>
       <c r="B4" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>95264522</v>
       </c>
       <c r="B5" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>95264049</v>
       </c>
       <c r="B6" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>95264194</v>
       </c>
       <c r="B7" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>95264257</v>
       </c>
       <c r="B8" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>95263872</v>
       </c>
       <c r="B9" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>95386244</v>
       </c>
       <c r="B10" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1851,7 +1851,7 @@
         <v>95386183</v>
       </c>
       <c r="B11" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1970,7 +1970,7 @@
         <v>95386114</v>
       </c>
       <c r="B12" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2094,7 +2094,7 @@
         <v>95386099</v>
       </c>
       <c r="B13" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2213,7 +2213,7 @@
         <v>95386259</v>
       </c>
       <c r="B14" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2332,7 +2332,7 @@
         <v>95386456</v>
       </c>
       <c r="B15" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2456,7 +2456,7 @@
         <v>95386154</v>
       </c>
       <c r="B16" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2580,7 +2580,7 @@
         <v>95386313</v>
       </c>
       <c r="B17" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2704,7 +2704,7 @@
         <v>95386133</v>
       </c>
       <c r="B18" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2828,7 +2828,7 @@
         <v>95386487</v>
       </c>
       <c r="B19" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2947,7 +2947,7 @@
         <v>95264356</v>
       </c>
       <c r="B20" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>95386500</v>
       </c>
       <c r="B21" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3204,7 +3204,7 @@
         <v>95386164</v>
       </c>
       <c r="B22" t="n">
-        <v>94805</v>
+        <v>95313</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3311,7 +3311,7 @@
         <v>95264703</v>
       </c>
       <c r="B23" t="n">
-        <v>94805</v>
+        <v>95313</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>95264424</v>
       </c>
       <c r="B24" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>95386390</v>
       </c>
       <c r="B25" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3688,7 +3688,7 @@
         <v>95386224</v>
       </c>
       <c r="B26" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3812,7 +3812,7 @@
         <v>95386517</v>
       </c>
       <c r="B27" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3936,7 +3936,7 @@
         <v>95263753</v>
       </c>
       <c r="B28" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4074,7 +4074,7 @@
         <v>95386200</v>
       </c>
       <c r="B29" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4193,7 +4193,7 @@
         <v>95386375</v>
       </c>
       <c r="B30" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
